--- a/Articoli unici.xlsx
+++ b/Articoli unici.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computer\Desktop\Progetti personali\In corso\Scontrini spese Lidl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95365274-911B-441A-8C76-963389E526D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517FF892-99A6-4139-98FA-A8E9FD345EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="400">
   <si>
     <t>Id articolo</t>
   </si>
@@ -32,160 +32,583 @@
     <t>Prodotto</t>
   </si>
   <si>
+    <t>ACCESSORI CUCINA-0539344</t>
+  </si>
+  <si>
+    <t>ACETO DI VINO BIANCO</t>
+  </si>
+  <si>
+    <t>ACQUA TONICA</t>
+  </si>
+  <si>
+    <t>AGLIO BIANCO</t>
+  </si>
+  <si>
+    <t>Aglio</t>
+  </si>
+  <si>
+    <t>AGLIO VOGHIERA DOP</t>
+  </si>
+  <si>
+    <t>ALBICOCCHE</t>
+  </si>
+  <si>
+    <t>Albicocche</t>
+  </si>
+  <si>
+    <t>ALBICOCCHE ROSSE</t>
+  </si>
+  <si>
+    <t>ALBICOCCHE SFUSE</t>
+  </si>
+  <si>
+    <t>ALBUME D'UOVO</t>
+  </si>
+  <si>
+    <t>ANGURIA A FETTE</t>
+  </si>
+  <si>
+    <t>Anguria</t>
+  </si>
+  <si>
+    <t>BABY ANGURIA</t>
+  </si>
+  <si>
+    <t>APFEL ROT SUB-SAUER</t>
+  </si>
+  <si>
+    <t>AVOCADO 700G</t>
+  </si>
+  <si>
+    <t>BANANE</t>
+  </si>
+  <si>
+    <t>BARR.CARAM BISCOTTO</t>
+  </si>
+  <si>
+    <t>Barrette</t>
+  </si>
+  <si>
+    <t>BARR.PROT CIOCCO BIA</t>
+  </si>
+  <si>
+    <t>BARRETTE PROT.CARAM</t>
+  </si>
+  <si>
+    <t>BISC- PROT.CIOCC.</t>
+  </si>
+  <si>
+    <t>BASE PER PINSA</t>
+  </si>
+  <si>
+    <t>COOKIES CIOCC VEGANO</t>
+  </si>
+  <si>
+    <t>Biscotti</t>
+  </si>
+  <si>
+    <t>DIGESTIVE OL.SEMI.GI</t>
+  </si>
+  <si>
+    <t>BORSA FRUTTA VERD.3€</t>
+  </si>
+  <si>
+    <t>CARPACCIO BRESAOLA</t>
+  </si>
+  <si>
+    <t>Bresaola</t>
+  </si>
+  <si>
+    <t>BURRO PAST LATTE ITA</t>
+  </si>
+  <si>
+    <t>Burro</t>
+  </si>
+  <si>
+    <t>CAFFE DECAFFEINATO</t>
+  </si>
+  <si>
+    <t>Caffè</t>
+  </si>
+  <si>
+    <t>CAFFE ROSSO</t>
+  </si>
+  <si>
+    <t>CAPPERI ACETO VINO</t>
+  </si>
+  <si>
+    <t>MACIN.DI BOV ADULTO</t>
+  </si>
+  <si>
+    <t>Carne macinata</t>
+  </si>
+  <si>
+    <t>MACIN.DI BOV.ADULTO</t>
+  </si>
+  <si>
+    <t>MACINATO DI BOVINO</t>
+  </si>
+  <si>
+    <t>MACINATO MAGRO</t>
+  </si>
+  <si>
+    <t>MACINATO MAIALE ITA</t>
+  </si>
+  <si>
+    <t>MACINATO MISTO</t>
+  </si>
+  <si>
+    <t>CAROTE XXL 1250G</t>
+  </si>
+  <si>
+    <t>Carote</t>
+  </si>
+  <si>
+    <t>CARTA DA FORNO</t>
+  </si>
+  <si>
+    <t>CARTA IGIEN 3 VELI</t>
+  </si>
+  <si>
+    <t>Carta Igienica</t>
+  </si>
+  <si>
+    <t>CARTA IGIENICA</t>
+  </si>
+  <si>
+    <t>CECI LESSATI</t>
+  </si>
+  <si>
+    <t>CIOCC LATT.AL CARAM</t>
+  </si>
+  <si>
+    <t>Cioccolato</t>
+  </si>
+  <si>
+    <t>CIPOLLA ROSSA</t>
+  </si>
+  <si>
+    <t>Cipolle</t>
+  </si>
+  <si>
+    <t>CIPOLLE DORATE</t>
+  </si>
+  <si>
+    <t>CIPOLLE DORATE 1KG</t>
+  </si>
+  <si>
+    <t>COUSCOUS ITALIANO</t>
+  </si>
+  <si>
+    <t>CREMA CORPO</t>
+  </si>
+  <si>
+    <t>CREMA DI ARACHIDI</t>
+  </si>
+  <si>
+    <t>Crema spalmabile</t>
+  </si>
+  <si>
+    <t>D.A.F. ALCOL ETILICO</t>
+  </si>
+  <si>
+    <t>DETERGENTE INTIMO</t>
+  </si>
+  <si>
+    <t>DG BOX CAP.CAFFE D.</t>
+  </si>
+  <si>
+    <t>GELAT.CARAMEL.SALATO</t>
+  </si>
+  <si>
+    <t>Dolci</t>
+  </si>
+  <si>
+    <t>GELATO COOKIES CREAM</t>
+  </si>
+  <si>
+    <t>KINDER PINGUI</t>
+  </si>
+  <si>
+    <t>RAFFAELLO GELATO</t>
+  </si>
+  <si>
+    <t>RICOTTADESSERT AMAR-</t>
+  </si>
+  <si>
+    <t>RISO AL LAT CILIEGIA</t>
+  </si>
+  <si>
+    <t>FAGIOLI BORLOTTI</t>
+  </si>
+  <si>
+    <t>FALAFEL</t>
+  </si>
+  <si>
+    <t>FARINA 00</t>
+  </si>
+  <si>
+    <t>FILETTI DI ALICI</t>
+  </si>
+  <si>
+    <t>FIOCCHI CON FR.ROSS</t>
+  </si>
+  <si>
+    <t>FETA GRECA DOP</t>
+  </si>
+  <si>
+    <t>Formaggio</t>
+  </si>
+  <si>
+    <t>CASEIF BRIZ- PROV BIA</t>
+  </si>
+  <si>
+    <t>FRAGOLE 250G</t>
+  </si>
+  <si>
+    <t>Fragole</t>
+  </si>
+  <si>
+    <t>FUNGHI INT IN OLIO</t>
+  </si>
+  <si>
+    <t>GNOCCHETTI</t>
+  </si>
+  <si>
+    <t>GOCCE DI CIOCCOLATO</t>
+  </si>
+  <si>
+    <t>GRANA PADANO DOP</t>
+  </si>
+  <si>
+    <t>Grana</t>
+  </si>
+  <si>
+    <t>GRANA PADANO DOP 12M</t>
+  </si>
+  <si>
+    <t>HUMMUS BARBABIETOLA</t>
+  </si>
+  <si>
+    <t>Hummus</t>
+  </si>
+  <si>
+    <t>HUMMUS PICCANTE</t>
+  </si>
+  <si>
+    <t>HUMMUS POMODORI SECC</t>
+  </si>
+  <si>
+    <t>RUCOLA BIO</t>
+  </si>
+  <si>
+    <t>Insalata</t>
+  </si>
+  <si>
+    <t>KIWI</t>
+  </si>
+  <si>
+    <t>LATTUGHINO</t>
+  </si>
+  <si>
+    <t>LIMONI SFUSI</t>
+  </si>
+  <si>
+    <t>LOGEX GUANTI M</t>
+  </si>
+  <si>
+    <t>MANDORLE PELATE</t>
+  </si>
+  <si>
+    <t>MANGO PZ</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>MARCATORE INDELE NER-0519204</t>
+  </si>
+  <si>
+    <t>MAZZO DI GERBERE</t>
+  </si>
+  <si>
+    <t>MELANZANE BIO</t>
+  </si>
+  <si>
+    <t>Melanzane</t>
+  </si>
+  <si>
+    <t>MELANZANE STRIATE</t>
+  </si>
+  <si>
+    <t>MELANZANE</t>
+  </si>
+  <si>
+    <t>MELE GOLDEN IGP</t>
+  </si>
+  <si>
+    <t>Mele</t>
+  </si>
+  <si>
+    <t>MELONE RETATO</t>
+  </si>
+  <si>
+    <t>Melone</t>
+  </si>
+  <si>
+    <t>MELONE MANTOVANO IGP</t>
+  </si>
+  <si>
+    <t>MISTO PER SOFFRITTO</t>
+  </si>
+  <si>
+    <t>MIX UVET MIRT.ROSSI</t>
+  </si>
+  <si>
+    <t>Mix frutta secca</t>
+  </si>
+  <si>
+    <t>MOZZ SENZA LATTOSIO</t>
+  </si>
+  <si>
+    <t>Mozzarella</t>
+  </si>
+  <si>
+    <t>MOZZAR.LATT ITALIAN-</t>
+  </si>
+  <si>
+    <t>MUFFIN CACAO</t>
+  </si>
+  <si>
+    <t>NIPPON QUADRATINI</t>
+  </si>
+  <si>
+    <t>NOCCIOL.DOLCE GUSTO</t>
+  </si>
+  <si>
+    <t>NOCI SGUSCIATE</t>
+  </si>
+  <si>
+    <t>OLIO PER FRIGGERE</t>
+  </si>
+  <si>
+    <t>OLIVE TAGGIASCHE DEN</t>
+  </si>
+  <si>
+    <t>Olive</t>
+  </si>
+  <si>
+    <t>OLIVE VERDI DENOCCIO</t>
+  </si>
+  <si>
+    <t>FILONE DI SEMOLA</t>
+  </si>
+  <si>
+    <t>Pane</t>
+  </si>
+  <si>
+    <t>PAGNOTTA PANE BIANCO</t>
+  </si>
+  <si>
+    <t>PANGRATTATO</t>
+  </si>
+  <si>
+    <t>Pangrattato</t>
+  </si>
+  <si>
+    <t>PASSA POMOD.BASILICO</t>
+  </si>
+  <si>
+    <t>Passata di pomodoro</t>
+  </si>
+  <si>
+    <t>POLPA DI POMOD.FINE</t>
+  </si>
+  <si>
+    <t>PASTA SFOGLIA</t>
+  </si>
+  <si>
+    <t>PATÈ SNACK GATTI</t>
+  </si>
+  <si>
+    <t>PEPERONI GIALLI</t>
+  </si>
+  <si>
+    <t>Peperoni</t>
+  </si>
+  <si>
+    <t>PEPERONI MISTI</t>
+  </si>
+  <si>
+    <t>PEPERONI ROSSI</t>
+  </si>
+  <si>
+    <t>NETTARINE</t>
+  </si>
+  <si>
+    <t>Pesche</t>
+  </si>
+  <si>
+    <t>PESCHE</t>
+  </si>
+  <si>
+    <t>PESCHE NETTARINE</t>
+  </si>
+  <si>
+    <t>PESCHE NOCI PIATTE</t>
+  </si>
+  <si>
+    <t>PESCHE PIATTE</t>
+  </si>
+  <si>
+    <t>PISELLI FINI SURGEL</t>
+  </si>
+  <si>
+    <t>POLVERE LIEVITANTE</t>
+  </si>
+  <si>
+    <t>POMODORI CILIEGINO</t>
+  </si>
+  <si>
+    <t>Pomodori</t>
+  </si>
+  <si>
+    <t>POMODORO CILIEGINO</t>
+  </si>
+  <si>
+    <t>POMODORO OBLUNGO</t>
+  </si>
+  <si>
+    <t>PORRI</t>
+  </si>
+  <si>
+    <t>PORTAPIL SETT BIANCO-0507563</t>
+  </si>
+  <si>
+    <t>PREZZEMOLO</t>
+  </si>
+  <si>
+    <t>QUARTIROLO LOMBARDO</t>
+  </si>
+  <si>
+    <t>RICOTTA FUSCELLA</t>
+  </si>
+  <si>
+    <t>Ricotta</t>
+  </si>
+  <si>
+    <t>SACCH.ORTOFR.BIOGRAD</t>
+  </si>
+  <si>
+    <t>SACCHETTI PATT BIANC</t>
+  </si>
+  <si>
+    <t>Sacchetti spazzatura</t>
+  </si>
+  <si>
+    <t>SACCHETTI PROF BAGNO</t>
+  </si>
+  <si>
+    <t>SACCHI SPAZZATU.130L</t>
+  </si>
+  <si>
+    <t>SCOTTEX FAZZOLETTI</t>
+  </si>
+  <si>
+    <t>SET PALETTA SCOPINO-0491718</t>
+  </si>
+  <si>
+    <t>SOVRACOSCE DI POLLO</t>
+  </si>
+  <si>
+    <t>Pollo</t>
+  </si>
+  <si>
+    <t>SPECK A FETTE</t>
+  </si>
+  <si>
+    <t>Speck</t>
+  </si>
+  <si>
+    <t>SPRAY/LACCA CLASSIC</t>
+  </si>
+  <si>
+    <t>STRACCH.SENZA LATT.</t>
+  </si>
+  <si>
+    <t>Stracchino</t>
+  </si>
+  <si>
+    <t>STRACCH.SENZA LATT_</t>
+  </si>
+  <si>
+    <t>STRACCHINO</t>
+  </si>
+  <si>
+    <t>STRACCH SENZA LATT.</t>
+  </si>
+  <si>
+    <t>SUCCO E POLPA PESCA</t>
+  </si>
+  <si>
+    <t>Succo</t>
+  </si>
+  <si>
+    <t>TAGLIOLINI ALL UOVO</t>
+  </si>
+  <si>
+    <t>TAVOLINO NERO FSC-051460</t>
+  </si>
+  <si>
+    <t>TONNO AL NATURALE</t>
+  </si>
+  <si>
+    <t>Tonno</t>
+  </si>
+  <si>
+    <t>TONNO NATURALE MSC</t>
+  </si>
+  <si>
+    <t>TONNO OLIO GIRASOLE</t>
+  </si>
+  <si>
+    <t>TRIANGOLINI MAIS BIO</t>
+  </si>
+  <si>
     <t>6 UOVA LOMB. TERRA L</t>
   </si>
   <si>
     <t>Uova</t>
   </si>
   <si>
-    <t>ACCESSORI CUCINA-0539344</t>
-  </si>
-  <si>
-    <t>ACETO DI VINO BIANCO</t>
-  </si>
-  <si>
-    <t>ACQUA TONICA</t>
-  </si>
-  <si>
-    <t>AGLIO BIANCO</t>
-  </si>
-  <si>
-    <t>Aglio</t>
-  </si>
-  <si>
-    <t>AGLIO VOGHIERA DOP</t>
-  </si>
-  <si>
-    <t>ALBICOCCHE</t>
-  </si>
-  <si>
-    <t>Albicocche</t>
-  </si>
-  <si>
-    <t>ALBICOCCHE ROSSE</t>
-  </si>
-  <si>
-    <t>ALBUME D'UOVO</t>
-  </si>
-  <si>
-    <t>ANGURIA A FETTE</t>
-  </si>
-  <si>
-    <t>Anguria</t>
-  </si>
-  <si>
-    <t>APFEL ROT SUB-SAUER</t>
-  </si>
-  <si>
-    <t>AVOCADO 700G</t>
-  </si>
-  <si>
-    <t>BABY ANGURIA</t>
-  </si>
-  <si>
-    <t>BANANE</t>
-  </si>
-  <si>
-    <t>BARR.CARAM BISCOTTO</t>
-  </si>
-  <si>
-    <t>Barrette</t>
-  </si>
-  <si>
-    <t>BARR.PROT CIOCCO BIA</t>
-  </si>
-  <si>
-    <t>BASE PER PINSA</t>
-  </si>
-  <si>
-    <t>BORSA FRUTTA VERD.3€</t>
-  </si>
-  <si>
-    <t>BURRO PAST LATTE ITA</t>
-  </si>
-  <si>
-    <t>Burro</t>
-  </si>
-  <si>
-    <t>CAFFE DECAFFEINATO</t>
-  </si>
-  <si>
-    <t>Caffè</t>
-  </si>
-  <si>
-    <t>CAFFE ROSSO</t>
-  </si>
-  <si>
-    <t>CAPPERI ACETO VINO</t>
-  </si>
-  <si>
-    <t>CARTA DA FORNO</t>
-  </si>
-  <si>
-    <t>CARTA IGIENICA</t>
-  </si>
-  <si>
-    <t>CECI LESSATI</t>
-  </si>
-  <si>
-    <t>CIOCC LATT.AL CARAM</t>
-  </si>
-  <si>
-    <t>Cioccolato</t>
-  </si>
-  <si>
-    <t>CIPOLLA ROSSA</t>
-  </si>
-  <si>
-    <t>Cipolle</t>
-  </si>
-  <si>
-    <t>CIPOLLE DORATE</t>
-  </si>
-  <si>
-    <t>CIPOLLE DORATE 1KG</t>
-  </si>
-  <si>
-    <t>COUSCOUS ITALIANO</t>
-  </si>
-  <si>
-    <t>CREMA CORPO</t>
-  </si>
-  <si>
-    <t>D.A.F. ALCOL ETILICO</t>
-  </si>
-  <si>
-    <t>DETERGENTE INTIMO</t>
-  </si>
-  <si>
-    <t>DG BOX CAP.CAFFE D.</t>
-  </si>
-  <si>
-    <t>FAGIOLI BORLOTTI</t>
-  </si>
-  <si>
-    <t>FALAFEL</t>
-  </si>
-  <si>
-    <t>FARINA 00</t>
-  </si>
-  <si>
-    <t>FETA GRECA DOP</t>
-  </si>
-  <si>
-    <t>Formaggio</t>
-  </si>
-  <si>
-    <t>FILETTI DI ALICI</t>
-  </si>
-  <si>
-    <t>FILONE DI SEMOLA</t>
-  </si>
-  <si>
-    <t>Pane</t>
-  </si>
-  <si>
-    <t>FIOCCHI CON FR.ROSS</t>
+    <t>UOVA ALLEV APERTO M</t>
+  </si>
+  <si>
+    <t>UOVA BIO</t>
+  </si>
+  <si>
+    <t>UVA BIANCA IGP 1KG</t>
+  </si>
+  <si>
+    <t>Uva</t>
+  </si>
+  <si>
+    <t>UVA SULTANINA</t>
+  </si>
+  <si>
+    <t>VASCHETTE 15</t>
+  </si>
+  <si>
+    <t>ORTRUGO DOC</t>
+  </si>
+  <si>
+    <t>Vino bianco</t>
+  </si>
+  <si>
+    <t>PROSECCO TREVISO DOC</t>
+  </si>
+  <si>
+    <t>TREBBIANO RUBICONE</t>
   </si>
   <si>
     <t>FRIULI DOP REFOSCO</t>
@@ -194,285 +617,12 @@
     <t>Vino rosso</t>
   </si>
   <si>
-    <t>FUNGHI INT IN OLIO</t>
-  </si>
-  <si>
-    <t>GELAT.CARAMEL.SALATO</t>
-  </si>
-  <si>
-    <t>Dolci</t>
-  </si>
-  <si>
-    <t>GELATO COOKIES CREAM</t>
-  </si>
-  <si>
-    <t>GNOCCHETTI</t>
-  </si>
-  <si>
-    <t>GOCCE DI CIOCCOLATO</t>
-  </si>
-  <si>
-    <t>GRANA PADANO DOP</t>
-  </si>
-  <si>
-    <t>Grana</t>
-  </si>
-  <si>
-    <t>GRANA PADANO DOP 12M</t>
-  </si>
-  <si>
-    <t>HUMMUS PICCANTE</t>
-  </si>
-  <si>
-    <t>Hummus</t>
-  </si>
-  <si>
-    <t>HUMMUS POMODORI SECC</t>
-  </si>
-  <si>
-    <t>KINDER PINGUI</t>
-  </si>
-  <si>
-    <t>KIWI</t>
-  </si>
-  <si>
-    <t>LATTUGHINO</t>
-  </si>
-  <si>
-    <t>LIMONI SFUSI</t>
-  </si>
-  <si>
-    <t>MACIN.DI BOV ADULTO</t>
-  </si>
-  <si>
-    <t>Carne macinata</t>
-  </si>
-  <si>
-    <t>MACIN.DI BOV.ADULTO</t>
-  </si>
-  <si>
-    <t>MACINATO DI BOVINO</t>
-  </si>
-  <si>
-    <t>MACINATO MAGRO</t>
-  </si>
-  <si>
-    <t>MACINATO MAIALE ITA</t>
-  </si>
-  <si>
-    <t>MACINATO MISTO</t>
-  </si>
-  <si>
-    <t>MARCATORE INDELE NER-0519204</t>
-  </si>
-  <si>
-    <t>MAZZO DI GERBERE</t>
-  </si>
-  <si>
-    <t>MELANZANE STRIATE</t>
-  </si>
-  <si>
-    <t>MELONE RETATO</t>
-  </si>
-  <si>
-    <t>MISTO PER SOFFRITTO</t>
-  </si>
-  <si>
-    <t>MIX UVET MIRT.ROSSI</t>
-  </si>
-  <si>
-    <t>MOZZ SENZA LATTOSIO</t>
-  </si>
-  <si>
-    <t>Mozzarella</t>
-  </si>
-  <si>
-    <t>MOZZAR.LATT ITALIAN-</t>
-  </si>
-  <si>
-    <t>MUFFIN CACAO</t>
-  </si>
-  <si>
-    <t>NETTARINE</t>
-  </si>
-  <si>
-    <t>Pesche</t>
-  </si>
-  <si>
-    <t>NIPPON QUADRATINI</t>
-  </si>
-  <si>
-    <t>NOCCIOL.DOLCE GUSTO</t>
-  </si>
-  <si>
-    <t>NOCI SGUSCIATE</t>
-  </si>
-  <si>
-    <t>OLIO PER FRIGGERE</t>
-  </si>
-  <si>
-    <t>OLIVE TAGGIASCHE DEN</t>
-  </si>
-  <si>
-    <t>ORTRUGO DOC</t>
-  </si>
-  <si>
-    <t>Vino bianco</t>
-  </si>
-  <si>
-    <t>PASSA POMOD.BASILICO</t>
-  </si>
-  <si>
-    <t>Passata di pomodoro</t>
-  </si>
-  <si>
-    <t>PASTA SFOGLIA</t>
-  </si>
-  <si>
-    <t>PATÈ SNACK GATTI</t>
-  </si>
-  <si>
-    <t>PEPERONI GIALLI</t>
-  </si>
-  <si>
-    <t>Peperoni</t>
-  </si>
-  <si>
-    <t>PEPERONI ROSSI</t>
-  </si>
-  <si>
-    <t>PESCHE</t>
-  </si>
-  <si>
-    <t>PESCHE NETTARINE</t>
-  </si>
-  <si>
-    <t>PESCHE NOCI PIATTE</t>
-  </si>
-  <si>
-    <t>PESCHE PIATTE</t>
-  </si>
-  <si>
-    <t>PISELLI FINI SURGEL</t>
-  </si>
-  <si>
-    <t>POLPA DI POMOD.FINE</t>
-  </si>
-  <si>
-    <t>POLVERE LIEVITANTE</t>
-  </si>
-  <si>
-    <t>POMODORI CILIEGINO</t>
-  </si>
-  <si>
-    <t>Pomodori</t>
-  </si>
-  <si>
-    <t>POMODORO CILIEGINO</t>
-  </si>
-  <si>
-    <t>POMODORO OBLUNGO</t>
-  </si>
-  <si>
-    <t>PORRI</t>
-  </si>
-  <si>
-    <t>PORTAPIL SETT BIANCO-0507563</t>
-  </si>
-  <si>
-    <t>PROSECCO TREVISO DOC</t>
-  </si>
-  <si>
-    <t>QUARTIROLO LOMBARDO</t>
-  </si>
-  <si>
-    <t>RAFFAELLO GELATO</t>
-  </si>
-  <si>
-    <t>RICOTTA FUSCELLA</t>
-  </si>
-  <si>
-    <t>Ricotta</t>
-  </si>
-  <si>
-    <t>RICOTTADESSERT AMAR-</t>
-  </si>
-  <si>
-    <t>RISO AL LAT CILIEGIA</t>
-  </si>
-  <si>
-    <t>SACCHETTI PATT BIANC</t>
-  </si>
-  <si>
-    <t>SACCHETTI PROF BAGNO</t>
-  </si>
-  <si>
-    <t>SACCHI SPAZZATU.130L</t>
-  </si>
-  <si>
-    <t>SET PALETTA SCOPINO-0491718</t>
-  </si>
-  <si>
-    <t>SOVRACOSCE DI POLLO</t>
-  </si>
-  <si>
-    <t>SPECK A FETTE</t>
-  </si>
-  <si>
-    <t>SPRAY/LACCA CLASSIC</t>
-  </si>
-  <si>
-    <t>STRACCH.SENZA LATT.</t>
-  </si>
-  <si>
-    <t>Stracchino</t>
-  </si>
-  <si>
-    <t>STRACCH.SENZA LATT_</t>
-  </si>
-  <si>
-    <t>STRACCHINO</t>
-  </si>
-  <si>
-    <t>TAGLIOLINI ALL UOVO</t>
-  </si>
-  <si>
-    <t>TONNO AL NATURALE</t>
-  </si>
-  <si>
-    <t>Tonno</t>
-  </si>
-  <si>
-    <t>TONNO NATURALE MSC</t>
-  </si>
-  <si>
-    <t>TONNO OLIO GIRASOLE</t>
-  </si>
-  <si>
-    <t>TREBBIANO RUBICONE</t>
-  </si>
-  <si>
-    <t>TRIANGOLINI MAIS BIO</t>
-  </si>
-  <si>
-    <t>UOVA ALLEV APERTO M</t>
-  </si>
-  <si>
-    <t>UOVA BIO</t>
-  </si>
-  <si>
-    <t>UVA BIANCA IGP 1KG</t>
-  </si>
-  <si>
-    <t>Uva</t>
-  </si>
-  <si>
-    <t>UVA SULTANINA</t>
-  </si>
-  <si>
     <t>VITEL TONNE</t>
   </si>
   <si>
+    <t>YOGURT BIANCO INTERO</t>
+  </si>
+  <si>
     <t>YOG INT BANANA</t>
   </si>
   <si>
@@ -488,21 +638,288 @@
     <t>YOG. INTERO VANIGLIA</t>
   </si>
   <si>
-    <t>YOGURT BIANCO INTERO</t>
-  </si>
-  <si>
     <t>YOGURT INT FRAGOLA</t>
   </si>
   <si>
     <t>YOGURT INTERO CAFFE</t>
   </si>
   <si>
+    <t>YOGURT INTERO COCCO</t>
+  </si>
+  <si>
     <t>YOGURT INTERO LIMONE</t>
   </si>
   <si>
     <t>ZUCCHERO SEMOLATO</t>
   </si>
   <si>
+    <t>6 UOVA LOMB TERRA L</t>
+  </si>
+  <si>
+    <t>ACE NETTARE IN BRICK</t>
+  </si>
+  <si>
+    <t>ALBICOCCHE 1KG</t>
+  </si>
+  <si>
+    <t>BARRETTE AL COCCO</t>
+  </si>
+  <si>
+    <t>BARRETTE PROT VANIG</t>
+  </si>
+  <si>
+    <t>BIO ZENZERO MANGO LI</t>
+  </si>
+  <si>
+    <t>Infuso</t>
+  </si>
+  <si>
+    <t>BIRRA DOPPIO MALTO</t>
+  </si>
+  <si>
+    <t>Birra</t>
+  </si>
+  <si>
+    <t>BISC. CER CIOCC</t>
+  </si>
+  <si>
+    <t>BISCOTTI RISO/LATTE</t>
+  </si>
+  <si>
+    <t>BOCCONCINI POLLO</t>
+  </si>
+  <si>
+    <t>CALVE MAIONESE</t>
+  </si>
+  <si>
+    <t>Maionese</t>
+  </si>
+  <si>
+    <t>CAPPUCCIO</t>
+  </si>
+  <si>
+    <t>Cappuccio</t>
+  </si>
+  <si>
+    <t>CAROTE BIO 500G</t>
+  </si>
+  <si>
+    <t>CILIEGIE 500G</t>
+  </si>
+  <si>
+    <t>Ciliegie</t>
+  </si>
+  <si>
+    <t>COCACOLA 0.5L</t>
+  </si>
+  <si>
+    <t>Coca Cola</t>
+  </si>
+  <si>
+    <t>CREMA ACETO BALSAM</t>
+  </si>
+  <si>
+    <t>Aceto</t>
+  </si>
+  <si>
+    <t>CROISSANT NOCCIOLA</t>
+  </si>
+  <si>
+    <t>Croissant</t>
+  </si>
+  <si>
+    <t>GOLEADOR CARAM FRUT</t>
+  </si>
+  <si>
+    <t>Goleador</t>
+  </si>
+  <si>
+    <t>INSALATA SFIZIOSA</t>
+  </si>
+  <si>
+    <t>LATTE PASTORIZZATO</t>
+  </si>
+  <si>
+    <t>Latte</t>
+  </si>
+  <si>
+    <t>LIBRO DI TESTO-0509061</t>
+  </si>
+  <si>
+    <t>Libro</t>
+  </si>
+  <si>
+    <t>MASCARPONE 41%GRASSI</t>
+  </si>
+  <si>
+    <t>Mascarpone</t>
+  </si>
+  <si>
+    <t>MELE GRANNY SMITH</t>
+  </si>
+  <si>
+    <t>MELONE GIALLO</t>
+  </si>
+  <si>
+    <t>MISTICANZA</t>
+  </si>
+  <si>
+    <t>Misticanza</t>
+  </si>
+  <si>
+    <t>MOZZAREL NO MANGIMI</t>
+  </si>
+  <si>
+    <t>OLIO D'OLIVA EXTRA</t>
+  </si>
+  <si>
+    <t>Olio</t>
+  </si>
+  <si>
+    <t>OLIO EXTRA VERG.BIO</t>
+  </si>
+  <si>
+    <t>OLIO SEMI ARACHIDE</t>
+  </si>
+  <si>
+    <t>Olio di semi</t>
+  </si>
+  <si>
+    <t>PAGNOTTA PROTEICA</t>
+  </si>
+  <si>
+    <t>PANE PITA</t>
+  </si>
+  <si>
+    <t>PASSATA POMOD.BIO</t>
+  </si>
+  <si>
+    <t>PEPERONI BUE SW. PAL</t>
+  </si>
+  <si>
+    <t>PESCHE 1KG</t>
+  </si>
+  <si>
+    <t>PESCHE NOCI 1KG</t>
+  </si>
+  <si>
+    <t>PETTO.TACCH.AL FORNO</t>
+  </si>
+  <si>
+    <t>Tacchino</t>
+  </si>
+  <si>
+    <t>POMODORI GRAPPOLO</t>
+  </si>
+  <si>
+    <t>POMODORO COKTAIL</t>
+  </si>
+  <si>
+    <t>PROVOLONE DOLCE</t>
+  </si>
+  <si>
+    <t>Provolone</t>
+  </si>
+  <si>
+    <t>RICOTTA</t>
+  </si>
+  <si>
+    <t>RUCOLA</t>
+  </si>
+  <si>
+    <t>Rucola</t>
+  </si>
+  <si>
+    <t>SCHWEPPES TONICA ZER</t>
+  </si>
+  <si>
+    <t>Schweppes</t>
+  </si>
+  <si>
+    <t>SENZA PECCATO MOUSSE</t>
+  </si>
+  <si>
+    <t>Mousse</t>
+  </si>
+  <si>
+    <t>SPECK AFFETT LIGHT</t>
+  </si>
+  <si>
+    <t>STRACCH.SENZA LATT</t>
+  </si>
+  <si>
+    <t>SUCCO D'ARANCIA</t>
+  </si>
+  <si>
+    <t>SUCCO DI MELA BIO</t>
+  </si>
+  <si>
+    <t>VALERIANA</t>
+  </si>
+  <si>
+    <t>Valeriana</t>
+  </si>
+  <si>
+    <t>YOG.INT BANANA</t>
+  </si>
+  <si>
+    <t>YOGURT INt FRAGOLA</t>
+  </si>
+  <si>
+    <t>CIOCC_ LATT.AL CARAM</t>
+  </si>
+  <si>
+    <t>MIX UVET MIRT_ ROSSI</t>
+  </si>
+  <si>
+    <t>MOZZAR.LATT.ITALIAN</t>
+  </si>
+  <si>
+    <t>SACCHETTI PATT_ BIANC</t>
+  </si>
+  <si>
+    <t>UOVA ALLEV.APERTO M</t>
+  </si>
+  <si>
+    <t>YOG INTERO VANIGLIA</t>
+  </si>
+  <si>
+    <t>AVOCADO PZ</t>
+  </si>
+  <si>
+    <t>FIOCCHI D'AVENA</t>
+  </si>
+  <si>
+    <t>MACIN DI BOV ADULTO</t>
+  </si>
+  <si>
+    <t>OLIO EXTRA VERG BIO</t>
+  </si>
+  <si>
+    <t>PANNA FRESCA PAST_</t>
+  </si>
+  <si>
+    <t>PAS SFOG ROTONDA</t>
+  </si>
+  <si>
+    <t>PROSC.CRUDO STAG_ 12M</t>
+  </si>
+  <si>
+    <t>PROVOLONE PICCANTE</t>
+  </si>
+  <si>
+    <t>SACCH ORTOFR.BIOGRAD</t>
+  </si>
+  <si>
+    <t>TONNO LEGGERO FAD FR</t>
+  </si>
+  <si>
+    <t>UVA BIANCA MAZZ. IGP</t>
+  </si>
+  <si>
+    <t>ZUCCHINE</t>
+  </si>
+  <si>
     <t>Categoria</t>
   </si>
   <si>
@@ -518,6 +935,12 @@
     <t>Articoli per la casa</t>
   </si>
   <si>
+    <t>Dispensa</t>
+  </si>
+  <si>
+    <t>Ingredienti per cucinare</t>
+  </si>
+  <si>
     <t>Aceto Di Vino Bianco</t>
   </si>
   <si>
@@ -557,9 +980,6 @@
     <t>Apfel Rot Sub-Sauer</t>
   </si>
   <si>
-    <t>Avocado 700G</t>
-  </si>
-  <si>
     <t>Banane</t>
   </si>
   <si>
@@ -569,18 +989,24 @@
     <t>Base Per Pinsa</t>
   </si>
   <si>
-    <t>Dispensa</t>
-  </si>
-  <si>
     <t>Pasta, riso, pane e cereali</t>
   </si>
   <si>
+    <t>Vino, birra e alcolici</t>
+  </si>
+  <si>
     <t>Borsa Frutta Verd.3€</t>
   </si>
   <si>
     <t>Frutta &amp; Verdura</t>
   </si>
   <si>
+    <t>Carne e Pesce</t>
+  </si>
+  <si>
+    <t>Salumi e affettati</t>
+  </si>
+  <si>
     <t>Latte, burro, panna e yogurt</t>
   </si>
   <si>
@@ -590,9 +1016,6 @@
     <t>Scatolame e barattoli</t>
   </si>
   <si>
-    <t>Carne e Pesce</t>
-  </si>
-  <si>
     <t>Carne fresca</t>
   </si>
   <si>
@@ -602,9 +1025,6 @@
     <t>Consumabili cucina</t>
   </si>
   <si>
-    <t>Carta Igienica</t>
-  </si>
-  <si>
     <t>Igiene e Cura Persona</t>
   </si>
   <si>
@@ -632,9 +1052,6 @@
     <t>Igiene</t>
   </si>
   <si>
-    <t>Dg Box Cap.Caffe D.</t>
-  </si>
-  <si>
     <t>Fagioli Borlotti</t>
   </si>
   <si>
@@ -647,18 +1064,12 @@
     <t>Farina 00</t>
   </si>
   <si>
-    <t>Ingredienti per cucinare</t>
-  </si>
-  <si>
     <t>Filetti Di Alici</t>
   </si>
   <si>
     <t>Pesce</t>
   </si>
   <si>
-    <t>Fiocchi Con Fr.Ross</t>
-  </si>
-  <si>
     <t>Biscotti e cereali</t>
   </si>
   <si>
@@ -674,15 +1085,33 @@
     <t>Gocce Di Cioccolato</t>
   </si>
   <si>
+    <t>Infusi e altre bevande</t>
+  </si>
+  <si>
     <t>Kiwi</t>
   </si>
   <si>
     <t>Lattughino</t>
   </si>
   <si>
+    <t>Altri prodotti</t>
+  </si>
+  <si>
     <t>Limoni Sfusi</t>
   </si>
   <si>
+    <t>Logex Guanti M</t>
+  </si>
+  <si>
+    <t>Altri consumabili pulizia</t>
+  </si>
+  <si>
+    <t>Mandorle Pelate</t>
+  </si>
+  <si>
+    <t>Frutta secca</t>
+  </si>
+  <si>
     <t>Marcatore Indele Ner-0519204</t>
   </si>
   <si>
@@ -692,42 +1121,24 @@
     <t>Fiori e piante</t>
   </si>
   <si>
-    <t>Melanzane Striate</t>
-  </si>
-  <si>
-    <t>Melone Retato</t>
-  </si>
-  <si>
     <t>Misto Per Soffritto</t>
   </si>
   <si>
     <t>Congelatore</t>
   </si>
   <si>
-    <t>Mix Uvet Mirt.Rossi</t>
-  </si>
-  <si>
-    <t>Frutta secca</t>
-  </si>
-  <si>
     <t>Muffin Cacao</t>
   </si>
   <si>
     <t>Nippon Quadratini</t>
   </si>
   <si>
-    <t>Nocciol.Dolce Gusto</t>
-  </si>
-  <si>
     <t>Noci Sgusciate</t>
   </si>
   <si>
     <t>Olio Per Friggere</t>
   </si>
   <si>
-    <t>Olive Taggiasche Den</t>
-  </si>
-  <si>
     <t>Pasta Sfoglia</t>
   </si>
   <si>
@@ -749,19 +1160,16 @@
     <t>Portapil Sett Bianco-0507563</t>
   </si>
   <si>
+    <t>Prezzemolo</t>
+  </si>
+  <si>
     <t>Quartirolo Lombardo</t>
   </si>
   <si>
-    <t>Sacchetti Patt Bianc</t>
-  </si>
-  <si>
-    <t>Sacchetti spazzatura</t>
-  </si>
-  <si>
-    <t>Sacchetti Prof Bagno</t>
-  </si>
-  <si>
-    <t>Sacchi Spazzatu.130L</t>
+    <t>Sacchetti frutta e verdura</t>
+  </si>
+  <si>
+    <t>Scottex Fazzoletti</t>
   </si>
   <si>
     <t>Set Paletta Scopino-0491718</t>
@@ -770,22 +1178,19 @@
     <t>Sovracosce Di Pollo</t>
   </si>
   <si>
-    <t>Speck A Fette</t>
-  </si>
-  <si>
-    <t>Salumi e affettati</t>
-  </si>
-  <si>
     <t>Spray/Lacca Classic</t>
   </si>
   <si>
     <t>Tagliolini All Uovo</t>
   </si>
   <si>
+    <t>Tavolino Nero Fsc-051460</t>
+  </si>
+  <si>
     <t>Triangolini Mais Bio</t>
   </si>
   <si>
-    <t>Vino, birra e alcolici</t>
+    <t>Vaschette 15</t>
   </si>
   <si>
     <t>Vitel Tonne</t>
@@ -795,6 +1200,27 @@
   </si>
   <si>
     <t>Zucchero Semolato</t>
+  </si>
+  <si>
+    <t>Avocado</t>
+  </si>
+  <si>
+    <t>Zucchine</t>
+  </si>
+  <si>
+    <t>Panna fresca</t>
+  </si>
+  <si>
+    <t>Pasta sfoglia</t>
+  </si>
+  <si>
+    <t>Prosciutto crudo</t>
+  </si>
+  <si>
+    <t>Sacchetti ortofrutta</t>
+  </si>
+  <si>
+    <t>Fiocchi D'Avena</t>
   </si>
 </sst>
 </file>
@@ -810,15 +1236,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -826,12 +1258,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,8 +1294,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tab_prodotti" displayName="tab_prodotti" ref="A1:C131" totalsRowShown="0">
-  <autoFilter ref="A1:C131" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tab_prodotti" displayName="tab_prodotti" ref="A1:C231" totalsRowShown="0">
+  <autoFilter ref="A1:C231" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C163">
+    <sortCondition ref="C1:C163"/>
+  </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id articolo"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Articolo"/>
@@ -862,10 +1309,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tab_categorie" displayName="tab_categorie" ref="A1:C88" totalsRowShown="0">
-  <autoFilter ref="A1:C88" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C89">
-    <sortCondition ref="A1:A89"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tab_categorie" displayName="tab_categorie" ref="A1:C126" totalsRowShown="0">
+  <autoFilter ref="A1:C126" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C126">
+    <sortCondition ref="A1:A127"/>
   </sortState>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Prodotto"/>
@@ -1161,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1182,93 +1629,93 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="C2" t="str">
+        <f>PROPER(B2)</f>
+        <v>Accessori Cucina-0539344</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="str">
         <f>PROPER(B3)</f>
-        <v>Accessori Cucina-0539344</v>
+        <v>Aceto Di Vino Bianco</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" t="str">
         <f>PROPER(B4)</f>
-        <v>Aceto Di Vino Bianco</v>
+        <v>Acqua Tonica</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
-      </c>
-      <c r="C5" t="str">
-        <f>PROPER(B5)</f>
-        <v>Acqua Tonica</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>7</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,7 +1723,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" t="str">
         <f>PROPER(B10)</f>
@@ -1288,45 +1735,44 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
         <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="str">
-        <f>PROPER(B12)</f>
-        <v>Apfel Rot Sub-Sauer</v>
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" t="str">
         <f>PROPER(B13)</f>
-        <v>Avocado 700G</v>
+        <v>Apfel Rot Sub-Sauer</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1334,7 +1780,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="str">
         <f>PROPER(B15)</f>
@@ -1346,10 +1792,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
         <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1357,758 +1803,746 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="str">
-        <f>PROPER(B18)</f>
-        <v>Base Per Pinsa</v>
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="str">
-        <f>PROPER(B19)</f>
-        <v>Borsa Frutta Verd.3€</v>
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="C20" t="str">
+        <f>PROPER(B20)</f>
+        <v>Base Per Pinsa</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C23" t="str">
         <f>PROPER(B23)</f>
-        <v>Capperi Aceto Vino</v>
+        <v>Borsa Frutta Verd.3€</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" t="str">
-        <f>PROPER(B24)</f>
-        <v>Carta Da Forno</v>
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
         <v>33</v>
-      </c>
-      <c r="C25" t="str">
-        <f>PROPER(B25)</f>
-        <v>Carta Igienica</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
       </c>
-      <c r="C26" t="str">
-        <f>PROPER(B26)</f>
-        <v>Ceci Lessati</v>
+      <c r="C26" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
         <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
         <v>37</v>
       </c>
-      <c r="C28" t="s">
-        <v>38</v>
+      <c r="C28" t="str">
+        <f>PROPER(B28)</f>
+        <v>Capperi Aceto Vino</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" t="s">
         <v>39</v>
-      </c>
-      <c r="C29" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
         <v>41</v>
       </c>
-      <c r="C31" t="str">
-        <f t="shared" ref="C31:C38" si="0">PROPER(B31)</f>
-        <v>Couscous Italiano</v>
+      <c r="C31" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
         <v>42</v>
       </c>
-      <c r="C32" t="str">
-        <f t="shared" si="0"/>
-        <v>Crema Corpo</v>
+      <c r="C32" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
       </c>
-      <c r="C33" t="str">
-        <f t="shared" si="0"/>
-        <v>D.A.F. Alcol Etilico</v>
+      <c r="C33" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
         <v>44</v>
       </c>
-      <c r="C34" t="str">
-        <f t="shared" si="0"/>
-        <v>Detergente Intimo</v>
+      <c r="C34" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="B35" t="s">
         <v>45</v>
       </c>
-      <c r="C35" t="str">
-        <f t="shared" si="0"/>
-        <v>Dg Box Cap.Caffe D.</v>
+      <c r="C35" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" t="str">
-        <f t="shared" si="0"/>
-        <v>Fagioli Borlotti</v>
+        <f>PROPER(B36)</f>
+        <v>Carta Da Forno</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>35</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="0"/>
-        <v>Falafel</v>
+        <v>48</v>
+      </c>
+      <c r="C37" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C38" t="str">
-        <f t="shared" si="0"/>
-        <v>Farina 00</v>
+        <f>PROPER(B38)</f>
+        <v>Carta Igienica</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="C39" t="str">
+        <f>PROPER(B39)</f>
+        <v>Ceci Lessati</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
-      </c>
-      <c r="C40" t="str">
-        <f>PROPER(B40)</f>
-        <v>Filetti Di Alici</v>
+        <v>52</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" t="str">
-        <f>PROPER(B42)</f>
-        <v>Fiocchi Con Fr.Ross</v>
+        <v>56</v>
+      </c>
+      <c r="C42" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
+        <v>57</v>
+      </c>
+      <c r="C43" t="s">
         <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C44" t="str">
         <f>PROPER(B44)</f>
-        <v>Funghi Int In Olio</v>
+        <v>Couscous Italiano</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" t="s">
         <v>59</v>
+      </c>
+      <c r="C45" t="str">
+        <f>PROPER(B45)</f>
+        <v>Crema Corpo</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="B46" t="s">
         <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C47" t="str">
         <f>PROPER(B47)</f>
-        <v>Gnocchetti</v>
+        <v>D.A.F. Alcol Etilico</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C48" t="str">
         <f>PROPER(B48)</f>
-        <v>Gocce Di Cioccolato</v>
+        <v>Detergente Intimo</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
         <v>65</v>
       </c>
       <c r="C50" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="s">
         <v>66</v>
-      </c>
-      <c r="C51" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>68</v>
       </c>
       <c r="C52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
         <v>69</v>
       </c>
       <c r="C53" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
         <v>70</v>
       </c>
-      <c r="C54" t="str">
-        <f>PROPER(B54)</f>
-        <v>Kiwi</v>
+      <c r="C54" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
         <v>71</v>
       </c>
-      <c r="C55" t="str">
-        <f>PROPER(B55)</f>
-        <v>Lattughino</v>
+      <c r="C55" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="B56" t="s">
         <v>72</v>
       </c>
       <c r="C56" t="str">
         <f>PROPER(B56)</f>
-        <v>Limoni Sfusi</v>
+        <v>Fagioli Borlotti</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
         <v>73</v>
       </c>
-      <c r="C57" t="s">
-        <v>74</v>
+      <c r="C57" t="str">
+        <f>PROPER(B57)</f>
+        <v>Falafel</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
-      </c>
-      <c r="C58" t="s">
         <v>74</v>
+      </c>
+      <c r="C58" t="str">
+        <f>PROPER(B58)</f>
+        <v>Farina 00</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="C59" t="str">
+        <f>PROPER(B59)</f>
+        <v>Filetti Di Alici</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C60" t="s">
-        <v>74</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B61" t="s">
+        <v>77</v>
+      </c>
+      <c r="C61" t="s">
         <v>78</v>
-      </c>
-      <c r="C61" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="B62" t="s">
         <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
         <v>80</v>
       </c>
-      <c r="C63" t="str">
-        <f t="shared" ref="C63:C68" si="1">PROPER(B63)</f>
-        <v>Marcatore Indele Ner-0519204</v>
+      <c r="C63" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C64" t="str">
-        <f t="shared" si="1"/>
-        <v>Mazzo Di Gerbere</v>
+        <f>PROPER(B64)</f>
+        <v>Funghi Int In Olio</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C65" t="str">
-        <f t="shared" si="1"/>
-        <v>Melanzane Striate</v>
+        <f>PROPER(B65)</f>
+        <v>Gnocchetti</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B66" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C66" t="str">
-        <f t="shared" si="1"/>
-        <v>Melone Retato</v>
+        <f>PROPER(B66)</f>
+        <v>Gocce Di Cioccolato</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
-      </c>
-      <c r="C67" t="str">
-        <f t="shared" si="1"/>
-        <v>Misto Per Soffritto</v>
+        <v>85</v>
+      </c>
+      <c r="C67" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B68" t="s">
-        <v>85</v>
-      </c>
-      <c r="C68" t="str">
-        <f t="shared" si="1"/>
-        <v>Mix Uvet Mirt.Rossi</v>
+        <v>87</v>
+      </c>
+      <c r="C68" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>67</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C69" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="B71" t="s">
+        <v>91</v>
+      </c>
+      <c r="C71" t="s">
         <v>89</v>
-      </c>
-      <c r="C71" t="str">
-        <f>PROPER(B71)</f>
-        <v>Muffin Cacao</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C72" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C73" t="str">
         <f>PROPER(B73)</f>
-        <v>Nippon Quadratini</v>
+        <v>Kiwi</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C74" t="str">
         <f>PROPER(B74)</f>
-        <v>Nocciol.Dolce Gusto</v>
+        <v>Lattughino</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C75" t="str">
         <f>PROPER(B75)</f>
-        <v>Noci Sgusciate</v>
+        <v>Limoni Sfusi</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>74</v>
+        <v>149</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C76" t="str">
         <f>PROPER(B76)</f>
-        <v>Olio Per Friggere</v>
+        <v>Logex Guanti M</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C77" t="str">
         <f>PROPER(B77)</f>
-        <v>Olive Taggiasche Den</v>
+        <v>Mandorle Pelate</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C78" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
-      </c>
-      <c r="C79" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="C79" t="str">
+        <f>PROPER(B79)</f>
+        <v>Marcatore Indele Ner-0519204</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C80" t="str">
         <f>PROPER(B80)</f>
-        <v>Pasta Sfoglia</v>
+        <v>Mazzo Di Gerbere</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
-      </c>
-      <c r="C81" t="str">
-        <f>PROPER(B81)</f>
-        <v>Patè Snack Gatti</v>
+        <v>103</v>
+      </c>
+      <c r="C81" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C82" t="s">
         <v>104</v>
@@ -2116,558 +2550,1666 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
-        <v>105</v>
-      </c>
-      <c r="C83" t="s">
-        <v>104</v>
+        <v>106</v>
+      </c>
+      <c r="C83" t="str">
+        <f>PROPER(B83)</f>
+        <v>Melanzane</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C84" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C85" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C86" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>109</v>
-      </c>
-      <c r="C87" t="s">
-        <v>91</v>
+        <v>112</v>
+      </c>
+      <c r="C87" t="str">
+        <f>PROPER(B87)</f>
+        <v>Misto Per Soffritto</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
-      </c>
-      <c r="C88" t="str">
-        <f>PROPER(B88)</f>
-        <v>Piselli Fini Surgel</v>
+        <v>113</v>
+      </c>
+      <c r="C88" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C89" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
-      </c>
-      <c r="C90" t="str">
-        <f>PROPER(B90)</f>
-        <v>Polvere Lievitante</v>
+        <v>117</v>
+      </c>
+      <c r="C90" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>113</v>
-      </c>
-      <c r="C91" t="s">
-        <v>114</v>
+        <v>118</v>
+      </c>
+      <c r="C91" t="str">
+        <f>PROPER(B91)</f>
+        <v>Muffin Cacao</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B92" t="s">
-        <v>115</v>
-      </c>
-      <c r="C92" t="s">
-        <v>114</v>
+        <v>119</v>
+      </c>
+      <c r="C92" t="str">
+        <f>PROPER(B92)</f>
+        <v>Nippon Quadratini</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B93" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="B94" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C94" t="str">
         <f>PROPER(B94)</f>
-        <v>Porri</v>
+        <v>Noci Sgusciate</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B95" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C95" t="str">
         <f>PROPER(B95)</f>
-        <v>Portapil Sett Bianco-0507563</v>
+        <v>Olio Per Friggere</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B96" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C96" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="B97" t="s">
-        <v>120</v>
-      </c>
-      <c r="C97" t="str">
-        <f>PROPER(B97)</f>
-        <v>Quartirolo Lombardo</v>
+        <v>125</v>
+      </c>
+      <c r="C97" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="B98" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C98" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="B99" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C99" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B100" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C100" t="s">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="B101" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="C101" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B102" t="s">
-        <v>126</v>
-      </c>
-      <c r="C102" t="str">
-        <f t="shared" ref="C102:C108" si="2">PROPER(B102)</f>
-        <v>Sacchetti Patt Bianc</v>
+        <v>133</v>
+      </c>
+      <c r="C102" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B103" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C103" t="str">
-        <f t="shared" si="2"/>
-        <v>Sacchetti Prof Bagno</v>
+        <f>PROPER(B103)</f>
+        <v>Pasta Sfoglia</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="B104" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C104" t="str">
-        <f t="shared" si="2"/>
-        <v>Sacchi Spazzatu.130L</v>
+        <f>PROPER(B104)</f>
+        <v>Patè Snack Gatti</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="B105" t="s">
-        <v>129</v>
-      </c>
-      <c r="C105" t="str">
-        <f t="shared" si="2"/>
-        <v>Set Paletta Scopino-0491718</v>
+        <v>136</v>
+      </c>
+      <c r="C105" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="B106" t="s">
-        <v>130</v>
-      </c>
-      <c r="C106" t="str">
-        <f t="shared" si="2"/>
-        <v>Sovracosce Di Pollo</v>
+        <v>138</v>
+      </c>
+      <c r="C106" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B107" t="s">
-        <v>131</v>
-      </c>
-      <c r="C107" t="str">
-        <f t="shared" si="2"/>
-        <v>Speck A Fette</v>
+        <v>139</v>
+      </c>
+      <c r="C107" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
-      </c>
-      <c r="C108" t="str">
-        <f t="shared" si="2"/>
-        <v>Spray/Lacca Classic</v>
+        <v>140</v>
+      </c>
+      <c r="C108" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="B109" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C109" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B110" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C110" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="B111" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C111" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="B112" t="s">
-        <v>137</v>
-      </c>
-      <c r="C112" t="str">
-        <f>PROPER(B112)</f>
-        <v>Tagliolini All Uovo</v>
+        <v>145</v>
+      </c>
+      <c r="C112" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B113" t="s">
-        <v>138</v>
-      </c>
-      <c r="C113" t="s">
-        <v>139</v>
+        <v>146</v>
+      </c>
+      <c r="C113" t="str">
+        <f>PROPER(B113)</f>
+        <v>Piselli Fini Surgel</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
-      </c>
-      <c r="C114" t="s">
-        <v>139</v>
+        <v>147</v>
+      </c>
+      <c r="C114" t="str">
+        <f>PROPER(B114)</f>
+        <v>Polvere Lievitante</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B115" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C115" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="B116" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C116" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B117" t="s">
-        <v>143</v>
-      </c>
-      <c r="C117" t="str">
-        <f>PROPER(B117)</f>
-        <v>Triangolini Mais Bio</v>
+        <v>151</v>
+      </c>
+      <c r="C117" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="B118" t="s">
-        <v>144</v>
-      </c>
-      <c r="C118" t="s">
-        <v>4</v>
+        <v>152</v>
+      </c>
+      <c r="C118" t="str">
+        <f>PROPER(B118)</f>
+        <v>Porri</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B119" t="s">
-        <v>145</v>
-      </c>
-      <c r="C119" t="s">
-        <v>4</v>
+        <v>153</v>
+      </c>
+      <c r="C119" t="str">
+        <f>PROPER(B119)</f>
+        <v>Portapil Sett Bianco-0507563</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="B120" t="s">
-        <v>146</v>
-      </c>
-      <c r="C120" t="s">
-        <v>147</v>
+        <v>154</v>
+      </c>
+      <c r="C120" t="str">
+        <f>PROPER(B120)</f>
+        <v>Prezzemolo</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B121" t="s">
-        <v>148</v>
-      </c>
-      <c r="C121" t="s">
-        <v>147</v>
+        <v>155</v>
+      </c>
+      <c r="C121" t="str">
+        <f>PROPER(B121)</f>
+        <v>Quartirolo Lombardo</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="B122" t="s">
-        <v>149</v>
-      </c>
-      <c r="C122" t="str">
-        <f>PROPER(B122)</f>
-        <v>Vitel Tonne</v>
+        <v>156</v>
+      </c>
+      <c r="C122" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="B123" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C123" t="s">
-        <v>151</v>
+        <v>398</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B124" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C124" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B125" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C125" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="B126" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="C126" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="B127" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C127" t="str">
         <f>PROPER(B127)</f>
-        <v>Yogurt Bianco Intero</v>
+        <v>Scottex Fazzoletti</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B128" t="s">
-        <v>156</v>
-      </c>
-      <c r="C128" t="s">
-        <v>151</v>
+        <v>164</v>
+      </c>
+      <c r="C128" t="str">
+        <f>PROPER(B128)</f>
+        <v>Set Paletta Scopino-0491718</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B129" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C129" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B130" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="C130" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="B131" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="C131" t="str">
         <f>PROPER(B131)</f>
+        <v>Spray/Lacca Classic</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>107</v>
+      </c>
+      <c r="B132" t="s">
+        <v>170</v>
+      </c>
+      <c r="C132" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>108</v>
+      </c>
+      <c r="B133" t="s">
+        <v>172</v>
+      </c>
+      <c r="C133" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>109</v>
+      </c>
+      <c r="B134" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>159</v>
+      </c>
+      <c r="B135" t="s">
+        <v>174</v>
+      </c>
+      <c r="C135" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>142</v>
+      </c>
+      <c r="B136" t="s">
+        <v>175</v>
+      </c>
+      <c r="C136" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>110</v>
+      </c>
+      <c r="B137" t="s">
+        <v>177</v>
+      </c>
+      <c r="C137" t="str">
+        <f>PROPER(B137)</f>
+        <v>Tagliolini All Uovo</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>160</v>
+      </c>
+      <c r="B138" t="s">
+        <v>178</v>
+      </c>
+      <c r="C138" t="str">
+        <f>PROPER(B138)</f>
+        <v>Tavolino Nero Fsc-051460</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>111</v>
+      </c>
+      <c r="B139" t="s">
+        <v>179</v>
+      </c>
+      <c r="C139" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>112</v>
+      </c>
+      <c r="B140" t="s">
+        <v>181</v>
+      </c>
+      <c r="C140" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>113</v>
+      </c>
+      <c r="B141" t="s">
+        <v>182</v>
+      </c>
+      <c r="C141" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>115</v>
+      </c>
+      <c r="B142" t="s">
+        <v>183</v>
+      </c>
+      <c r="C142" t="str">
+        <f>PROPER(B142)</f>
+        <v>Triangolini Mais Bio</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
+        <v>184</v>
+      </c>
+      <c r="C143" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>116</v>
+      </c>
+      <c r="B144" t="s">
+        <v>186</v>
+      </c>
+      <c r="C144" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>117</v>
+      </c>
+      <c r="B145" t="s">
+        <v>187</v>
+      </c>
+      <c r="C145" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>118</v>
+      </c>
+      <c r="B146" t="s">
+        <v>188</v>
+      </c>
+      <c r="C146" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>119</v>
+      </c>
+      <c r="B147" t="s">
+        <v>190</v>
+      </c>
+      <c r="C147" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>161</v>
+      </c>
+      <c r="B148" t="s">
+        <v>191</v>
+      </c>
+      <c r="C148" t="str">
+        <f>PROPER(B148)</f>
+        <v>Vaschette 15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>76</v>
+      </c>
+      <c r="B149" t="s">
+        <v>192</v>
+      </c>
+      <c r="C149" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>94</v>
+      </c>
+      <c r="B150" t="s">
+        <v>194</v>
+      </c>
+      <c r="C150" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>114</v>
+      </c>
+      <c r="B151" t="s">
+        <v>195</v>
+      </c>
+      <c r="C151" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>41</v>
+      </c>
+      <c r="B152" t="s">
+        <v>196</v>
+      </c>
+      <c r="C152" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>120</v>
+      </c>
+      <c r="B153" t="s">
+        <v>198</v>
+      </c>
+      <c r="C153" t="str">
+        <f>PROPER(B153)</f>
+        <v>Vitel Tonne</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>125</v>
+      </c>
+      <c r="B154" t="s">
+        <v>199</v>
+      </c>
+      <c r="C154" t="str">
+        <f>PROPER(B154)</f>
+        <v>Yogurt Bianco Intero</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>121</v>
+      </c>
+      <c r="B155" t="s">
+        <v>200</v>
+      </c>
+      <c r="C155" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>122</v>
+      </c>
+      <c r="B156" t="s">
+        <v>202</v>
+      </c>
+      <c r="C156" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>123</v>
+      </c>
+      <c r="B157" t="s">
+        <v>203</v>
+      </c>
+      <c r="C157" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>124</v>
+      </c>
+      <c r="B158" t="s">
+        <v>204</v>
+      </c>
+      <c r="C158" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>126</v>
+      </c>
+      <c r="B159" t="s">
+        <v>205</v>
+      </c>
+      <c r="C159" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>127</v>
+      </c>
+      <c r="B160" t="s">
+        <v>206</v>
+      </c>
+      <c r="C160" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>143</v>
+      </c>
+      <c r="B161" t="s">
+        <v>207</v>
+      </c>
+      <c r="C161" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>128</v>
+      </c>
+      <c r="B162" t="s">
+        <v>208</v>
+      </c>
+      <c r="C162" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>129</v>
+      </c>
+      <c r="B163" t="s">
+        <v>209</v>
+      </c>
+      <c r="C163" t="str">
+        <f>PROPER(B163)</f>
         <v>Zucchero Semolato</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164" t="s">
+        <v>210</v>
+      </c>
+      <c r="C164" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165" t="s">
+        <v>211</v>
+      </c>
+      <c r="C165" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166" t="s">
+        <v>212</v>
+      </c>
+      <c r="C166" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167" t="s">
+        <v>213</v>
+      </c>
+      <c r="C167" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168" t="s">
+        <v>214</v>
+      </c>
+      <c r="C168" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169" t="s">
+        <v>215</v>
+      </c>
+      <c r="C169" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170" t="s">
+        <v>217</v>
+      </c>
+      <c r="C170" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171" t="s">
+        <v>219</v>
+      </c>
+      <c r="C171" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172" t="s">
+        <v>220</v>
+      </c>
+      <c r="C172" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173" t="s">
+        <v>221</v>
+      </c>
+      <c r="C173" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174" t="s">
+        <v>222</v>
+      </c>
+      <c r="C174" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175" t="s">
+        <v>224</v>
+      </c>
+      <c r="C175" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176" t="s">
+        <v>226</v>
+      </c>
+      <c r="C176" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177" t="s">
+        <v>227</v>
+      </c>
+      <c r="C177" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178" t="s">
+        <v>229</v>
+      </c>
+      <c r="C178" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179" t="s">
+        <v>231</v>
+      </c>
+      <c r="C179" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180" t="s">
+        <v>233</v>
+      </c>
+      <c r="C180" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181" t="s">
+        <v>235</v>
+      </c>
+      <c r="C181" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182" t="s">
+        <v>237</v>
+      </c>
+      <c r="C182" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183" t="s">
+        <v>238</v>
+      </c>
+      <c r="C183" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184" t="s">
+        <v>240</v>
+      </c>
+      <c r="C184" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185" t="s">
+        <v>242</v>
+      </c>
+      <c r="C185" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186" t="s">
+        <v>244</v>
+      </c>
+      <c r="C186" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187" t="s">
+        <v>245</v>
+      </c>
+      <c r="C187" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188" t="s">
+        <v>246</v>
+      </c>
+      <c r="C188" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189" t="s">
+        <v>248</v>
+      </c>
+      <c r="C189" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190" t="s">
+        <v>249</v>
+      </c>
+      <c r="C190" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191" t="s">
+        <v>251</v>
+      </c>
+      <c r="C191" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192" t="s">
+        <v>252</v>
+      </c>
+      <c r="C192" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193" t="s">
+        <v>254</v>
+      </c>
+      <c r="C193" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194" t="s">
+        <v>255</v>
+      </c>
+      <c r="C194" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195" t="s">
+        <v>256</v>
+      </c>
+      <c r="C195" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196" t="s">
+        <v>257</v>
+      </c>
+      <c r="C196" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197" t="s">
+        <v>258</v>
+      </c>
+      <c r="C197" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198" t="s">
+        <v>259</v>
+      </c>
+      <c r="C198" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199" t="s">
+        <v>260</v>
+      </c>
+      <c r="C199" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200" t="s">
+        <v>262</v>
+      </c>
+      <c r="C200" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201" t="s">
+        <v>263</v>
+      </c>
+      <c r="C201" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202" t="s">
+        <v>264</v>
+      </c>
+      <c r="C202" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203" t="s">
+        <v>266</v>
+      </c>
+      <c r="C203" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204" t="s">
+        <v>267</v>
+      </c>
+      <c r="C204" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205" t="s">
+        <v>269</v>
+      </c>
+      <c r="C205" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206" t="s">
+        <v>271</v>
+      </c>
+      <c r="C206" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207" t="s">
+        <v>273</v>
+      </c>
+      <c r="C207" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208" t="s">
+        <v>274</v>
+      </c>
+      <c r="C208" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209" t="s">
+        <v>275</v>
+      </c>
+      <c r="C209" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210" t="s">
+        <v>276</v>
+      </c>
+      <c r="C210" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211" t="s">
+        <v>277</v>
+      </c>
+      <c r="C211" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212" t="s">
+        <v>279</v>
+      </c>
+      <c r="C212" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213" t="s">
+        <v>280</v>
+      </c>
+      <c r="C213" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214" t="s">
+        <v>281</v>
+      </c>
+      <c r="C214" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215" t="s">
+        <v>282</v>
+      </c>
+      <c r="C215" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216" t="s">
+        <v>283</v>
+      </c>
+      <c r="C216" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217" t="s">
+        <v>284</v>
+      </c>
+      <c r="C217" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218" t="s">
+        <v>285</v>
+      </c>
+      <c r="C218" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219" t="s">
+        <v>286</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220" t="s">
+        <v>287</v>
+      </c>
+      <c r="C220" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221" t="s">
+        <v>288</v>
+      </c>
+      <c r="C221" t="str">
+        <f>PROPER(B221)</f>
+        <v>Fiocchi D'Avena</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222" t="s">
+        <v>289</v>
+      </c>
+      <c r="C222" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223" t="s">
+        <v>290</v>
+      </c>
+      <c r="C223" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224" t="s">
+        <v>291</v>
+      </c>
+      <c r="C224" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225" t="s">
+        <v>292</v>
+      </c>
+      <c r="C225" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226" t="s">
+        <v>293</v>
+      </c>
+      <c r="C226" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227" t="s">
+        <v>294</v>
+      </c>
+      <c r="C227" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228" t="s">
+        <v>295</v>
+      </c>
+      <c r="C228" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229" t="s">
+        <v>296</v>
+      </c>
+      <c r="C229" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230" t="s">
+        <v>297</v>
+      </c>
+      <c r="C230" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231" t="s">
+        <v>298</v>
+      </c>
+      <c r="C231" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -2680,7 +4222,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -2693,967 +4235,1385 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>160</v>
+        <v>299</v>
       </c>
       <c r="C1" t="s">
-        <v>161</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>302</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>304</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>306</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>309</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="C8" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>312</v>
       </c>
       <c r="C9" t="s">
-        <v>170</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>318</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>310</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>179</v>
+        <v>393</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C12" t="s">
-        <v>180</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>184</v>
+        <v>321</v>
       </c>
       <c r="B14" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>310</v>
       </c>
       <c r="C15" t="s">
-        <v>186</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>302</v>
       </c>
       <c r="C16" t="s">
-        <v>180</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>324</v>
       </c>
       <c r="B17" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>326</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>191</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="C19" t="s">
-        <v>192</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>194</v>
+        <v>302</v>
       </c>
       <c r="C20" t="s">
-        <v>195</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>329</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C21" t="s">
-        <v>188</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C22" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>326</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>197</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>332</v>
       </c>
       <c r="B25" t="s">
-        <v>194</v>
+        <v>302</v>
       </c>
       <c r="C25" t="s">
-        <v>199</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>334</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>201</v>
+        <v>336</v>
       </c>
       <c r="B27" t="s">
-        <v>194</v>
+        <v>304</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C28" t="s">
-        <v>180</v>
+        <v>314</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>302</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>204</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C30" t="s">
-        <v>188</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>310</v>
       </c>
       <c r="C31" t="s">
-        <v>206</v>
+        <v>311</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C32" t="s">
-        <v>208</v>
+        <v>322</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>334</v>
       </c>
       <c r="C33" t="s">
-        <v>210</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>211</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>304</v>
       </c>
       <c r="C34" t="s">
-        <v>212</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>234</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c r="C35" t="s">
-        <v>213</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>214</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>307</v>
       </c>
       <c r="C36" t="s">
-        <v>188</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>341</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>334</v>
       </c>
       <c r="C37" t="s">
-        <v>176</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>182</v>
+        <v>302</v>
       </c>
       <c r="C38" t="s">
-        <v>208</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>343</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>330</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="C40" t="s">
-        <v>206</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>217</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>326</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>348</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C43" t="s">
-        <v>173</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="B44" t="s">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="C44" t="s">
-        <v>164</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>221</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
-        <v>222</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>223</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>330</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>316</v>
       </c>
       <c r="C47" t="s">
-        <v>173</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>225</v>
+        <v>353</v>
       </c>
       <c r="B48" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="C48" t="s">
-        <v>226</v>
+        <v>305</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B49" t="s">
-        <v>171</v>
+        <v>302</v>
       </c>
       <c r="C49" t="s">
-        <v>228</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B50" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="C50" t="s">
-        <v>213</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>229</v>
+        <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="C51" t="s">
-        <v>180</v>
+        <v>345</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>310</v>
       </c>
       <c r="C52" t="s">
-        <v>180</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C53" t="s">
-        <v>180</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>232</v>
+        <v>355</v>
       </c>
       <c r="B54" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="C54" t="s">
-        <v>228</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s">
-        <v>182</v>
+        <v>316</v>
       </c>
       <c r="C55" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>234</v>
+        <v>356</v>
       </c>
       <c r="B56" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C56" t="s">
-        <v>188</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s">
-        <v>182</v>
+        <v>302</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>357</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>358</v>
       </c>
       <c r="B58" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C58" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>235</v>
+        <v>359</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>307</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>360</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="C60" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>104</v>
+        <v>361</v>
       </c>
       <c r="B61" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>362</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="C62" t="s">
-        <v>173</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>238</v>
+        <v>363</v>
       </c>
       <c r="B63" t="s">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c r="C63" t="s">
-        <v>226</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
-        <v>182</v>
+        <v>316</v>
       </c>
       <c r="C64" t="s">
-        <v>208</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>364</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>302</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>365</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>240</v>
+        <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>312</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>313</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="C67" t="s">
-        <v>164</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="C68" t="s">
-        <v>213</v>
+        <v>314</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>247</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="C69" t="s">
-        <v>213</v>
+        <v>313</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>243</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s">
-        <v>166</v>
+        <v>316</v>
       </c>
       <c r="C70" t="s">
-        <v>244</v>
+        <v>367</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>245</v>
+        <v>114</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>312</v>
       </c>
       <c r="C71" t="s">
-        <v>244</v>
+        <v>362</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>302</v>
       </c>
       <c r="C72" t="s">
-        <v>244</v>
+        <v>320</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>116</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="C73" t="s">
-        <v>164</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>368</v>
       </c>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>302</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>249</v>
+        <v>369</v>
       </c>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>302</v>
       </c>
       <c r="C75" t="s">
-        <v>250</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>251</v>
+        <v>370</v>
       </c>
       <c r="B76" t="s">
-        <v>194</v>
+        <v>312</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="C77" t="s">
-        <v>213</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="C78" t="s">
-        <v>176</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>371</v>
       </c>
       <c r="B79" t="s">
-        <v>189</v>
+        <v>304</v>
       </c>
       <c r="C79" t="s">
-        <v>210</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>304</v>
       </c>
       <c r="C80" t="s">
-        <v>180</v>
+        <v>330</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>4</v>
+        <v>127</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="C81" t="s">
-        <v>176</v>
+        <v>322</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="C82" t="s">
-        <v>173</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>98</v>
+        <v>395</v>
       </c>
       <c r="B83" t="s">
-        <v>169</v>
+        <v>316</v>
       </c>
       <c r="C83" t="s">
-        <v>254</v>
+        <v>328</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="B84" t="s">
-        <v>169</v>
+        <v>304</v>
       </c>
       <c r="C84" t="s">
-        <v>254</v>
+        <v>305</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>255</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s">
-        <v>189</v>
+        <v>316</v>
       </c>
       <c r="C85" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>373</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>302</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>374</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>312</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>313</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="B88" t="s">
-        <v>182</v>
+        <v>312</v>
       </c>
       <c r="C88" t="s">
-        <v>208</v>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>375</v>
+      </c>
+      <c r="B89" t="s">
+        <v>316</v>
+      </c>
+      <c r="C89" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" t="s">
+        <v>326</v>
+      </c>
+      <c r="C90" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>376</v>
+      </c>
+      <c r="B91" t="s">
+        <v>304</v>
+      </c>
+      <c r="C91" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>149</v>
+      </c>
+      <c r="B92" t="s">
+        <v>312</v>
+      </c>
+      <c r="C92" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>377</v>
+      </c>
+      <c r="B93" t="s">
+        <v>312</v>
+      </c>
+      <c r="C93" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>378</v>
+      </c>
+      <c r="B94" t="s">
+        <v>302</v>
+      </c>
+      <c r="C94" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>379</v>
+      </c>
+      <c r="B95" t="s">
+        <v>312</v>
+      </c>
+      <c r="C95" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>397</v>
+      </c>
+      <c r="B96" t="s">
+        <v>326</v>
+      </c>
+      <c r="C96" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>265</v>
+      </c>
+      <c r="B97" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>380</v>
+      </c>
+      <c r="B98" t="s">
+        <v>316</v>
+      </c>
+      <c r="C98" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>157</v>
+      </c>
+      <c r="B99" t="s">
+        <v>316</v>
+      </c>
+      <c r="C99" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>268</v>
+      </c>
+      <c r="B100" t="s">
+        <v>312</v>
+      </c>
+      <c r="C100" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>398</v>
+      </c>
+      <c r="B101" t="s">
+        <v>312</v>
+      </c>
+      <c r="C101" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>160</v>
+      </c>
+      <c r="B102" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>270</v>
+      </c>
+      <c r="B103" t="s">
+        <v>310</v>
+      </c>
+      <c r="C103" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>382</v>
+      </c>
+      <c r="B104" t="s">
+        <v>334</v>
+      </c>
+      <c r="C104" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>383</v>
+      </c>
+      <c r="B105" t="s">
+        <v>302</v>
+      </c>
+      <c r="C105" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>384</v>
+      </c>
+      <c r="B106" t="s">
+        <v>326</v>
+      </c>
+      <c r="C106" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>168</v>
+      </c>
+      <c r="B107" t="s">
+        <v>326</v>
+      </c>
+      <c r="C107" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>385</v>
+      </c>
+      <c r="B108" t="s">
+        <v>334</v>
+      </c>
+      <c r="C108" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>171</v>
+      </c>
+      <c r="B109" t="s">
+        <v>316</v>
+      </c>
+      <c r="C109" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>176</v>
+      </c>
+      <c r="B110" t="s">
+        <v>310</v>
+      </c>
+      <c r="C110" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>261</v>
+      </c>
+      <c r="B111" t="s">
+        <v>326</v>
+      </c>
+      <c r="C111" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>386</v>
+      </c>
+      <c r="B112" t="s">
+        <v>316</v>
+      </c>
+      <c r="C112" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>387</v>
+      </c>
+      <c r="B113" t="s">
+        <v>302</v>
+      </c>
+      <c r="C113" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>180</v>
+      </c>
+      <c r="B114" t="s">
+        <v>326</v>
+      </c>
+      <c r="C114" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>388</v>
+      </c>
+      <c r="B115" t="s">
+        <v>302</v>
+      </c>
+      <c r="C115" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>185</v>
+      </c>
+      <c r="B116" t="s">
+        <v>316</v>
+      </c>
+      <c r="C116" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>189</v>
+      </c>
+      <c r="B117" t="s">
+        <v>312</v>
+      </c>
+      <c r="C117" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>278</v>
+      </c>
+      <c r="B118" t="s">
+        <v>312</v>
+      </c>
+      <c r="C118" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>389</v>
+      </c>
+      <c r="B119" t="s">
+        <v>302</v>
+      </c>
+      <c r="C119" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>193</v>
+      </c>
+      <c r="B120" t="s">
+        <v>310</v>
+      </c>
+      <c r="C120" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>197</v>
+      </c>
+      <c r="B121" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>390</v>
+      </c>
+      <c r="B122" t="s">
+        <v>326</v>
+      </c>
+      <c r="C122" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>391</v>
+      </c>
+      <c r="B123" t="s">
+        <v>316</v>
+      </c>
+      <c r="C123" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>201</v>
+      </c>
+      <c r="B124" t="s">
+        <v>316</v>
+      </c>
+      <c r="C124" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>392</v>
+      </c>
+      <c r="B125" t="s">
+        <v>304</v>
+      </c>
+      <c r="C125" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>394</v>
+      </c>
+      <c r="B126" t="s">
+        <v>312</v>
+      </c>
+      <c r="C126" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
